--- a/provider_specialty_cprd_V.0.3.xlsx
+++ b/provider_specialty_cprd_V.0.3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms0952_ox_ac_uk/Documents/OMOP_Validation study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{F8CCD673-2DB1-4E4C-9864-DE09D412825F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6F79DE3-16A6-4522-B854-4B86C655F6D8}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{F8CCD673-2DB1-4E4C-9864-DE09D412825F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16CFFAE8-499D-44E6-95A6-32DBD2ED093F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2735BDA3-DE0F-409A-AF31-62DE8638BF76}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2735BDA3-DE0F-409A-AF31-62DE8638BF76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -753,7 +753,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1179,18 +1179,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AFD464E-EA38-4A90-94D9-A0751CC594C3}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E199"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" customWidth="1"/>
-    <col min="4" max="4" width="70.7109375" customWidth="1"/>
-    <col min="5" max="5" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.88671875" customWidth="1"/>
+    <col min="4" max="4" width="70.6640625" customWidth="1"/>
+    <col min="5" max="5" width="39.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1207,7 +1206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1225,7 +1224,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1243,7 +1242,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1261,7 +1260,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1269,7 +1268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -1277,7 +1276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1285,7 +1284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -1296,7 +1295,7 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -1304,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -1312,7 +1311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
@@ -1329,7 +1328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1337,7 +1336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1348,7 +1347,7 @@
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" hidden="1">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1356,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -1364,7 +1363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1375,7 +1374,7 @@
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="1:5" hidden="1">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -1383,7 +1382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
@@ -1400,7 +1399,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
@@ -1417,7 +1416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -1425,7 +1424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>30</v>
       </c>
@@ -1442,7 +1441,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
@@ -1458,7 +1457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>33</v>
       </c>
@@ -1475,7 +1474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>34</v>
       </c>
@@ -1486,7 +1485,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5" hidden="1">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>35</v>
       </c>
@@ -1494,7 +1493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>36</v>
       </c>
@@ -1505,7 +1504,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:5" hidden="1">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
@@ -1513,7 +1512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>38</v>
       </c>
@@ -1521,7 +1520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>39</v>
       </c>
@@ -1532,7 +1531,7 @@
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>40</v>
       </c>
@@ -1549,7 +1548,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>41</v>
       </c>
@@ -1557,7 +1556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>42</v>
       </c>
@@ -1574,7 +1573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>43</v>
       </c>
@@ -1582,7 +1581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>44</v>
       </c>
@@ -1590,7 +1589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>45</v>
       </c>
@@ -1598,7 +1597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>46</v>
       </c>
@@ -1606,7 +1605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>47</v>
       </c>
@@ -1614,7 +1613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>48</v>
       </c>
@@ -1622,7 +1621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>49</v>
       </c>
@@ -1639,7 +1638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>50</v>
       </c>
@@ -1647,7 +1646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>51</v>
       </c>
@@ -1655,7 +1654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>52</v>
       </c>
@@ -1672,7 +1671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>53</v>
       </c>
@@ -1689,7 +1688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>54</v>
       </c>
@@ -1697,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>55</v>
       </c>
@@ -1714,7 +1713,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>57</v>
       </c>
@@ -1731,7 +1730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>59</v>
       </c>
@@ -1745,7 +1744,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>60</v>
       </c>
@@ -1762,7 +1761,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>61</v>
       </c>
@@ -1776,7 +1775,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>62</v>
       </c>
@@ -1790,7 +1789,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>63</v>
       </c>
@@ -1798,7 +1797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>64</v>
       </c>
@@ -1809,7 +1808,7 @@
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>65</v>
       </c>
@@ -1826,7 +1825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>66</v>
       </c>
@@ -1843,7 +1842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>67</v>
       </c>
@@ -1860,7 +1859,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>68</v>
       </c>
@@ -1877,7 +1876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>70</v>
       </c>
@@ -1885,7 +1884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>71</v>
       </c>
@@ -1902,7 +1901,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>73</v>
       </c>
@@ -1910,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>74</v>
       </c>
@@ -1918,7 +1917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>75</v>
       </c>
@@ -1926,7 +1925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>76</v>
       </c>
@@ -1944,7 +1943,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>78</v>
       </c>
@@ -1962,7 +1961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>79</v>
       </c>
@@ -1980,7 +1979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>80</v>
       </c>
@@ -1988,12 +1987,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B67" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>81</v>
       </c>
@@ -2001,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>82</v>
       </c>
@@ -2009,7 +2008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>83</v>
       </c>
@@ -2017,7 +2016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>84</v>
       </c>
@@ -2035,7 +2034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>85</v>
       </c>
@@ -2053,7 +2052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>86</v>
       </c>
@@ -2071,7 +2070,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>87</v>
       </c>
@@ -2079,7 +2078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>88</v>
       </c>
@@ -2087,7 +2086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>89</v>
       </c>
@@ -2095,7 +2094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>90</v>
       </c>
@@ -2103,7 +2102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>91</v>
       </c>
@@ -2121,7 +2120,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>92</v>
       </c>
@@ -2129,7 +2128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>93</v>
       </c>
@@ -2137,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>94</v>
       </c>
@@ -2154,7 +2153,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>97</v>
       </c>
@@ -2162,7 +2161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>98</v>
       </c>
@@ -2179,7 +2178,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>99</v>
       </c>
@@ -2196,7 +2195,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>100</v>
       </c>
@@ -2213,7 +2212,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>101</v>
       </c>
@@ -2230,7 +2229,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>102</v>
       </c>
@@ -2247,7 +2246,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>103</v>
       </c>
@@ -2264,7 +2263,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>104</v>
       </c>
@@ -2281,7 +2280,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>105</v>
       </c>
@@ -2289,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>106</v>
       </c>
@@ -2306,7 +2305,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>107</v>
       </c>
@@ -2314,7 +2313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>108</v>
       </c>
@@ -2331,7 +2330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>109</v>
       </c>
@@ -2348,7 +2347,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>110</v>
       </c>
@@ -2356,7 +2355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>111</v>
       </c>
@@ -2373,7 +2372,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>112</v>
       </c>
@@ -2381,7 +2380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>113</v>
       </c>
@@ -2398,7 +2397,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>114</v>
       </c>
@@ -2415,7 +2414,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>115</v>
       </c>
@@ -2432,7 +2431,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>116</v>
       </c>
@@ -2449,7 +2448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>117</v>
       </c>
@@ -2457,7 +2456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>118</v>
       </c>
@@ -2474,7 +2473,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>119</v>
       </c>
@@ -2491,7 +2490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>120</v>
       </c>
@@ -2508,7 +2507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>121</v>
       </c>
@@ -2516,7 +2515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>122</v>
       </c>
@@ -2533,7 +2532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>124</v>
       </c>
@@ -2541,7 +2540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>125</v>
       </c>
@@ -2549,7 +2548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>126</v>
       </c>
@@ -2557,7 +2556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>127</v>
       </c>
@@ -2574,7 +2573,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>128</v>
       </c>
@@ -2591,7 +2590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>130</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>131</v>
       </c>
@@ -2607,7 +2606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>132</v>
       </c>
@@ -2615,7 +2614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>133</v>
       </c>
@@ -2623,7 +2622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>134</v>
       </c>
@@ -2631,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>135</v>
       </c>
@@ -2648,7 +2647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>136</v>
       </c>
@@ -2665,7 +2664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>137</v>
       </c>
@@ -2682,7 +2681,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>138</v>
       </c>
@@ -2699,7 +2698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>140</v>
       </c>
@@ -2707,7 +2706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>141</v>
       </c>
@@ -2724,7 +2723,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>142</v>
       </c>
@@ -2741,7 +2740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>143</v>
       </c>
@@ -2758,7 +2757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>144</v>
       </c>
@@ -2766,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>145</v>
       </c>
@@ -2783,7 +2782,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>146</v>
       </c>
@@ -2800,7 +2799,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>147</v>
       </c>
@@ -2817,7 +2816,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>148</v>
       </c>
@@ -2834,7 +2833,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>149</v>
       </c>
@@ -2842,7 +2841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>150</v>
       </c>
@@ -2850,7 +2849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>151</v>
       </c>
@@ -2867,7 +2866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>152</v>
       </c>
@@ -2875,7 +2874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>153</v>
       </c>
@@ -2892,7 +2891,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>154</v>
       </c>
@@ -2903,7 +2902,7 @@
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
     </row>
-    <row r="137" spans="1:5" hidden="1">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>155</v>
       </c>
@@ -2911,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>156</v>
       </c>
@@ -2928,7 +2927,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>158</v>
       </c>
@@ -2936,7 +2935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>159</v>
       </c>
@@ -2944,7 +2943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:5" hidden="1">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>160</v>
       </c>
@@ -2952,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>161</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:5" hidden="1">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>162</v>
       </c>
@@ -2968,7 +2967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>163</v>
       </c>
@@ -2985,7 +2984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>164</v>
       </c>
@@ -3002,7 +3001,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>165</v>
       </c>
@@ -3010,7 +3009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>166</v>
       </c>
@@ -3027,7 +3026,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>167</v>
       </c>
@@ -3035,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>168</v>
       </c>
@@ -3043,7 +3042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>169</v>
       </c>
@@ -3051,7 +3050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>170</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>171</v>
       </c>
@@ -3076,7 +3075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>172</v>
       </c>
@@ -3093,7 +3092,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>173</v>
       </c>
@@ -3110,7 +3109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>175</v>
       </c>
@@ -3127,7 +3126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>177</v>
       </c>
@@ -3144,7 +3143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>178</v>
       </c>
@@ -3161,7 +3160,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>179</v>
       </c>
@@ -3169,7 +3168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>180</v>
       </c>
@@ -3186,7 +3185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>181</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>182</v>
       </c>
@@ -3211,7 +3210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>183</v>
       </c>
@@ -3219,7 +3218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>184</v>
       </c>
@@ -3236,7 +3235,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>185</v>
       </c>
@@ -3247,7 +3246,7 @@
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>186</v>
       </c>
@@ -3264,7 +3263,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>187</v>
       </c>
@@ -3272,7 +3271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>188</v>
       </c>
@@ -3280,7 +3279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>189</v>
       </c>
@@ -3288,7 +3287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>190</v>
       </c>
@@ -3296,7 +3295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>191</v>
       </c>
@@ -3313,7 +3312,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>192</v>
       </c>
@@ -3330,7 +3329,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>193</v>
       </c>
@@ -3338,7 +3337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:5" hidden="1">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>194</v>
       </c>
@@ -3346,7 +3345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>195</v>
       </c>
@@ -3354,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>196</v>
       </c>
@@ -3371,7 +3370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>197</v>
       </c>
@@ -3379,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>198</v>
       </c>
@@ -3387,7 +3386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>199</v>
       </c>
@@ -3395,7 +3394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
         <v>200</v>
       </c>
@@ -3412,7 +3411,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:5" hidden="1">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>201</v>
       </c>
@@ -3420,7 +3419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>202</v>
       </c>
@@ -3437,7 +3436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>204</v>
       </c>
@@ -3454,7 +3453,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>205</v>
       </c>
@@ -3465,7 +3464,7 @@
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
     </row>
-    <row r="184" spans="1:5" hidden="1">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>206</v>
       </c>
@@ -3473,7 +3472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>207</v>
       </c>
@@ -3484,7 +3483,7 @@
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
     </row>
-    <row r="186" spans="1:5" hidden="1">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>208</v>
       </c>
@@ -3492,7 +3491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
         <v>209</v>
       </c>
@@ -3509,7 +3508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>210</v>
       </c>
@@ -3526,7 +3525,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>211</v>
       </c>
@@ -3534,7 +3533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>212</v>
       </c>
@@ -3542,7 +3541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>213</v>
       </c>
@@ -3550,7 +3549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
         <v>214</v>
       </c>
@@ -3567,7 +3566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>215</v>
       </c>
@@ -3584,7 +3583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>217</v>
       </c>
@@ -3592,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
         <v>218</v>
       </c>
@@ -3609,7 +3608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>220</v>
       </c>
@@ -3617,7 +3616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>221</v>
       </c>
@@ -3625,7 +3624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>222</v>
       </c>
@@ -3633,7 +3632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
         <v>223</v>
       </c>
@@ -3651,13 +3650,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E199" xr:uid="{4AFD464E-EA38-4A90-94D9-A0751CC594C3}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E199" xr:uid="{4AFD464E-EA38-4A90-94D9-A0751CC594C3}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
